--- a/data/dividends_info_20260714.xlsx
+++ b/data/dividends_info_20260714.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>61.58000183105469</v>
+        <v>61.36000061035156</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1461513434944608</v>
+        <v>0.1466753570807768</v>
       </c>
       <c r="J2" t="n">
         <v>244</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>64.65000152587891</v>
+        <v>65.09999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.082753261374318</v>
+        <v>1.075268842407527</v>
       </c>
       <c r="J3" t="n">
         <v>223</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.579999923706055</v>
+        <v>9.340000152587891</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6263048066579608</v>
+        <v>0.6423982764430194</v>
       </c>
       <c r="J4" t="n">
         <v>153</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>61.58000183105469</v>
+        <v>61.36000061035156</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1461513434944608</v>
+        <v>0.1466753570807768</v>
       </c>
       <c r="J6" t="n">
         <v>153</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.115000009536743</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="I7" t="n">
-        <v>3.640661922118176</v>
+        <v>3.598130664738818</v>
       </c>
       <c r="J7" t="n">
         <v>132</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>21.95499992370605</v>
+        <v>21.70000076293945</v>
       </c>
       <c r="I8" t="n">
-        <v>1.229788207416324</v>
+        <v>1.244239587590808</v>
       </c>
       <c r="J8" t="n">
         <v>132</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.019999980926514</v>
+        <v>6.130000114440918</v>
       </c>
       <c r="I9" t="n">
-        <v>3.322259146738715</v>
+        <v>3.262642679709653</v>
       </c>
       <c r="J9" t="n">
         <v>125</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.940000057220459</v>
+        <v>6.059999942779541</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8417508336421938</v>
+        <v>0.8250825160415183</v>
       </c>
       <c r="J12" t="n">
         <v>83</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.880000114440918</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7786885063291337</v>
+        <v>0.7755101889880786</v>
       </c>
       <c r="J13" t="n">
         <v>76</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21.95499992370605</v>
+        <v>21.70000076293945</v>
       </c>
       <c r="I14" t="n">
-        <v>1.229788207416324</v>
+        <v>1.244239587590808</v>
       </c>
       <c r="J14" t="n">
         <v>69</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>61.58000183105469</v>
+        <v>61.36000061035156</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1461513434944608</v>
+        <v>0.1466753570807768</v>
       </c>
       <c r="J15" t="n">
         <v>69</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5.860000133514404</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I16" t="n">
-        <v>5.119453808272897</v>
+        <v>5.08474568052218</v>
       </c>
       <c r="J16" t="n">
         <v>62</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4.880000114440918</v>
+        <v>4.900000095367432</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7786885063291337</v>
+        <v>0.7755101889880786</v>
       </c>
       <c r="J18" t="n">
         <v>20</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.840000152587891</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="I19" t="n">
-        <v>4.280821805958635</v>
+        <v>4.302926032050844</v>
       </c>
       <c r="J19" t="n">
         <v>13</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>4.28000020980835</v>
+        <v>4.289999961853027</v>
       </c>
       <c r="I20" t="n">
-        <v>3.27102787703529</v>
+        <v>3.263403292421668</v>
       </c>
       <c r="J20" t="n">
         <v>6</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>10.22599983215332</v>
+        <v>10.27999973297119</v>
       </c>
       <c r="I21" t="n">
-        <v>2.542538668761654</v>
+        <v>2.529182945074388</v>
       </c>
       <c r="J21" t="n">
         <v>6</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>14.4399995803833</v>
+        <v>14.27999973297119</v>
       </c>
       <c r="I22" t="n">
-        <v>4.155124774484746</v>
+        <v>4.201680750838221</v>
       </c>
       <c r="J22" t="n">
         <v>6</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2.818000078201294</v>
+        <v>2.829999923706055</v>
       </c>
       <c r="I23" t="n">
-        <v>7.806955070789925</v>
+        <v>7.77385179968121</v>
       </c>
       <c r="J23" t="n">
         <v>6</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>6.775000095367432</v>
+        <v>6.809999942779541</v>
       </c>
       <c r="I25" t="n">
-        <v>3.542435374489599</v>
+        <v>3.52422910450191</v>
       </c>
       <c r="J25" t="n">
         <v>6</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>19</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="I26" t="n">
-        <v>1.978947368421053</v>
+        <v>1.968586348117482</v>
       </c>
       <c r="J26" t="n">
         <v>6</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3.099999904632568</v>
+        <v>3.140000104904175</v>
       </c>
       <c r="I30" t="n">
-        <v>4.838709826275912</v>
+        <v>4.777069904097268</v>
       </c>
       <c r="J30" t="n">
         <v>-1</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2.220000028610229</v>
+        <v>2.180000066757202</v>
       </c>
       <c r="I31" t="n">
-        <v>3.828828779484834</v>
+        <v>3.899082449407415</v>
       </c>
       <c r="J31" t="n">
         <v>-8</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4.699999809265137</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="I32" t="n">
-        <v>1.489361762568769</v>
+        <v>1.476793320255521</v>
       </c>
       <c r="J32" t="n">
         <v>-8</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>35.84999847412109</v>
+        <v>36</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4184100596497374</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="J33" t="n">
         <v>-8</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.199999809265137</v>
+        <v>5.150000095367432</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7692307974459868</v>
+        <v>0.7766990147433418</v>
       </c>
       <c r="J35" t="n">
         <v>-15</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>21.54000091552734</v>
+        <v>21.5</v>
       </c>
       <c r="I36" t="n">
-        <v>1.16063133414161</v>
+        <v>1.162790697674419</v>
       </c>
       <c r="J36" t="n">
         <v>-22</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>28.20000076293945</v>
+        <v>28</v>
       </c>
       <c r="I37" t="n">
-        <v>0.6914893429941666</v>
+        <v>0.6964285714285714</v>
       </c>
       <c r="J37" t="n">
         <v>-22</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5.054999828338623</v>
+        <v>5.074999809265137</v>
       </c>
       <c r="I39" t="n">
-        <v>5.73689435901151</v>
+        <v>5.714285929047003</v>
       </c>
       <c r="J39" t="n">
         <v>-22</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3.822000026702881</v>
+        <v>3.875999927520752</v>
       </c>
       <c r="I40" t="n">
-        <v>4.186289871327578</v>
+        <v>4.127967053455095</v>
       </c>
       <c r="J40" t="n">
         <v>-22</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>2.54200005531311</v>
+        <v>2.565999984741211</v>
       </c>
       <c r="I41" t="n">
-        <v>5.452399566644697</v>
+        <v>5.401402993927852</v>
       </c>
       <c r="J41" t="n">
         <v>-22</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>50.15999984741211</v>
+        <v>51</v>
       </c>
       <c r="I42" t="n">
-        <v>1.255980865064742</v>
+        <v>1.235294117647059</v>
       </c>
       <c r="J42" t="n">
         <v>-22</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.119999885559082</v>
+        <v>6.175000190734863</v>
       </c>
       <c r="I43" t="n">
-        <v>2.287581742123032</v>
+        <v>2.267206407702785</v>
       </c>
       <c r="J43" t="n">
         <v>-22</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>28.52000045776367</v>
+        <v>28.59000015258789</v>
       </c>
       <c r="I45" t="n">
-        <v>2.980364608544788</v>
+        <v>2.973067490253442</v>
       </c>
       <c r="J45" t="n">
         <v>-22</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>61.58000183105469</v>
+        <v>61.36000061035156</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1461513434944608</v>
+        <v>0.1466753570807768</v>
       </c>
       <c r="J46" t="n">
         <v>-22</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>1.519999980926514</v>
+        <v>1.490000009536743</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6578947450975963</v>
+        <v>0.6711409353016787</v>
       </c>
       <c r="J47" t="n">
         <v>-22</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>6.165999889373779</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I48" t="n">
-        <v>2.940317924955605</v>
+        <v>2.924193638346076</v>
       </c>
       <c r="J48" t="n">
         <v>-22</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>9.449999809265137</v>
+        <v>9.510000228881836</v>
       </c>
       <c r="I49" t="n">
-        <v>2.751322806854305</v>
+        <v>2.733964182360174</v>
       </c>
       <c r="J49" t="n">
         <v>-22</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>10.25500011444092</v>
+        <v>10.32999992370605</v>
       </c>
       <c r="I50" t="n">
-        <v>2.701121374049848</v>
+        <v>2.681510184373959</v>
       </c>
       <c r="J50" t="n">
         <v>-22</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.940000057220459</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="I52" t="n">
-        <v>3.741496525819677</v>
+        <v>3.703703668025653</v>
       </c>
       <c r="J52" t="n">
         <v>-29</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1.620000004768372</v>
+        <v>1.629999995231628</v>
       </c>
       <c r="I53" t="n">
-        <v>1.481481477120831</v>
+        <v>1.47239264234412</v>
       </c>
       <c r="J53" t="n">
         <v>-29</v>
@@ -3935,7 +3935,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3945,14 +3945,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3962,14 +3962,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4037,7 +4037,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4200,14 +4200,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4224,7 +4224,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4234,14 +4234,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4258,7 +4258,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4275,7 +4275,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4428,7 +4428,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -4445,7 +4445,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -4455,14 +4455,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -4472,14 +4472,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -4489,14 +4489,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -4506,14 +4506,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -4523,14 +4523,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -4547,7 +4547,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4557,14 +4557,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4574,14 +4574,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4615,7 +4615,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4625,14 +4625,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4642,14 +4642,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4659,14 +4659,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4676,14 +4676,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4700,7 +4700,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4727,14 +4727,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4744,14 +4744,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4778,14 +4778,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4819,7 +4819,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4836,7 +4836,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4853,7 +4853,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4863,14 +4863,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4880,14 +4880,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4904,7 +4904,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4914,14 +4914,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4931,14 +4931,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4965,14 +4965,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4982,14 +4982,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4999,14 +4999,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5016,14 +5016,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5040,7 +5040,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5067,14 +5067,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5084,14 +5084,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5101,14 +5101,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5125,7 +5125,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5135,14 +5135,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5159,7 +5159,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5169,14 +5169,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5210,7 +5210,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5237,14 +5237,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5295,7 +5295,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5305,14 +5305,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5329,7 +5329,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5339,14 +5339,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5363,7 +5363,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5373,14 +5373,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5390,14 +5390,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5407,14 +5407,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5424,14 +5424,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5448,7 +5448,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5458,14 +5458,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5482,7 +5482,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5492,14 +5492,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5509,14 +5509,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5526,14 +5526,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5560,14 +5560,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5577,14 +5577,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5594,14 +5594,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5611,14 +5611,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5645,14 +5645,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5669,7 +5669,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5696,14 +5696,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5720,7 +5720,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5730,14 +5730,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5747,14 +5747,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5764,14 +5764,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5788,7 +5788,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5832,14 +5832,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5873,7 +5873,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5890,7 +5890,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5900,14 +5900,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5917,14 +5917,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5934,14 +5934,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5951,14 +5951,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6026,7 +6026,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6036,14 +6036,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6053,14 +6053,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6104,14 +6104,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6121,14 +6121,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6155,14 +6155,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6172,14 +6172,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6189,14 +6189,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6206,14 +6206,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6223,14 +6223,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6247,7 +6247,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6257,14 +6257,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6281,7 +6281,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6298,7 +6298,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6308,14 +6308,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6342,14 +6342,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6366,7 +6366,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6383,7 +6383,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6434,7 +6434,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6451,7 +6451,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6468,7 +6468,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6485,7 +6485,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6502,7 +6502,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6519,7 +6519,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6563,14 +6563,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6587,7 +6587,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6604,7 +6604,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6621,7 +6621,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6631,14 +6631,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6648,14 +6648,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6672,7 +6672,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6682,14 +6682,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6706,7 +6706,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6716,14 +6716,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6733,14 +6733,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6750,14 +6750,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -6791,7 +6791,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
@@ -6846,61 +6846,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Preliminary Results</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>